--- a/backtest_runs/20260410_193731/by_symbol/AABS/AABS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AABS/AABS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-227.3600000000042</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>99772.64</v>
@@ -679,7 +679,7 @@
         <v>-6787.159999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>92985.48</v>
@@ -725,7 +725,7 @@
         <v>-6734.959999999994</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>86250.52</v>
@@ -863,7 +863,7 @@
         <v>-6429.880000000007</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>84244.87999999999</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>84244.87999999999</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>90894</v>
@@ -1185,7 +1185,7 @@
         <v>-288.8400000000011</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92640.95999999999</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>93983.08</v>
@@ -1369,7 +1369,7 @@
         <v>-415.2800000000047</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>93567.79999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-3507.840000000001</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>92541.2</v>
